--- a/E/EG1B.xlsx
+++ b/E/EG1B.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="60">
   <si>
     <t/>
   </si>
   <si>
-    <t>20042991</t>
-  </si>
-  <si>
-    <t>IDM GULA PSR PRM 1KG</t>
+    <t>20138236</t>
+  </si>
+  <si>
+    <t>CHEETOS JGG BKR 120G</t>
   </si>
   <si>
     <t>EG1B</t>
@@ -28,184 +28,169 @@
     <t>1</t>
   </si>
   <si>
-    <t>PT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20052296</t>
-  </si>
-  <si>
-    <t>IDM GULA PRM KNG 1KG</t>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20138241</t>
+  </si>
+  <si>
+    <t>CHEETOS KEJU 120G</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>10008882</t>
-  </si>
-  <si>
-    <t>K/API KOPI SPCL 150G</t>
+    <t>20138231</t>
+  </si>
+  <si>
+    <t>DORITOS SMB SALSA120</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>10005491</t>
-  </si>
-  <si>
-    <t>TONG TJI JASM T/A.25</t>
+    <t>20139538</t>
+  </si>
+  <si>
+    <t>LAYS RMPT LAUT 105G</t>
+  </si>
+  <si>
+    <t>20071780</t>
+  </si>
+  <si>
+    <t>POTABEE CHIP BBQ 65G</t>
+  </si>
+  <si>
+    <t>RT,(E-0.5B)</t>
+  </si>
+  <si>
+    <t>20071781</t>
+  </si>
+  <si>
+    <t>POTABEE CHIP SWD 65G</t>
+  </si>
+  <si>
+    <t>20057730</t>
+  </si>
+  <si>
+    <t>TIC TIC STCK BWNG 70</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>20133375</t>
-  </si>
-  <si>
-    <t>VSLNE LOT FLWLESS100</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20138898</t>
-  </si>
-  <si>
-    <t>SNSLK SHP S.SMTH 160</t>
-  </si>
-  <si>
-    <t>20138022</t>
-  </si>
-  <si>
-    <t>SNSLK CRMBTH S.SL 30</t>
-  </si>
-  <si>
-    <t>20060386</t>
-  </si>
-  <si>
-    <t>GIV BW MLB&amp;CLG PC400</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20131028</t>
-  </si>
-  <si>
-    <t>ZINC SHP LMN MINT340</t>
+    <t>10000348</t>
+  </si>
+  <si>
+    <t>DK KACANG 180G</t>
+  </si>
+  <si>
+    <t>10026501</t>
+  </si>
+  <si>
+    <t>DK KACANG SUKRO 95G</t>
+  </si>
+  <si>
+    <t>20084707</t>
+  </si>
+  <si>
+    <t>SUKRO KC OVEN BWG 95</t>
+  </si>
+  <si>
+    <t>20056958</t>
+  </si>
+  <si>
+    <t>QTELA TEMPE R/LAUT55</t>
+  </si>
+  <si>
+    <t>RT,(E-14H)</t>
+  </si>
+  <si>
+    <t>20132871</t>
+  </si>
+  <si>
+    <t>DK RONI RS.CORN 135G</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>20137792</t>
-  </si>
-  <si>
-    <t>MAMA LIME GREEN 690</t>
+    <t>20020018</t>
+  </si>
+  <si>
+    <t>HATARI S.H.PUFF 245G</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20028585</t>
+  </si>
+  <si>
+    <t>MI GEMEZ ENAK PREM22</t>
+  </si>
+  <si>
+    <t>20045175</t>
+  </si>
+  <si>
+    <t>CHA CHA MILK CHO 20G</t>
+  </si>
+  <si>
+    <t>20001396</t>
+  </si>
+  <si>
+    <t>S/Q BITE CASHEW 30G</t>
+  </si>
+  <si>
+    <t>10004502</t>
+  </si>
+  <si>
+    <t>CC BIG BABOL T.FRT20</t>
+  </si>
+  <si>
+    <t>20065180</t>
+  </si>
+  <si>
+    <t>GLICO PEJOY CHO 30G</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>RT,(E-1.5B)</t>
-  </si>
-  <si>
-    <t>10000341</t>
-  </si>
-  <si>
-    <t>DUA KELINCI KCG 370G</t>
-  </si>
-  <si>
-    <t>20115362</t>
-  </si>
-  <si>
-    <t>CHUBA KRP BALADO 125</t>
-  </si>
-  <si>
-    <t>20072194</t>
-  </si>
-  <si>
-    <t>MH MAITOS S.BLDO 140</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20122289</t>
-  </si>
-  <si>
-    <t>BONCABE MK LV2 NC135</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20056977</t>
-  </si>
-  <si>
-    <t>GARUDA ROSTA BWG 95</t>
-  </si>
-  <si>
-    <t>20089490</t>
-  </si>
-  <si>
-    <t>GARUDA ROSTA PDS 90G</t>
-  </si>
-  <si>
-    <t>20139132</t>
-  </si>
-  <si>
-    <t>GRUDA RS.MAX B&amp;S 80G</t>
-  </si>
-  <si>
-    <t>20092875</t>
-  </si>
-  <si>
-    <t>GRUDA PILUS MI GR 80</t>
-  </si>
-  <si>
-    <t>20127483</t>
-  </si>
-  <si>
-    <t>GRUDA PILUS RDNG 80</t>
-  </si>
-  <si>
-    <t>20071797</t>
-  </si>
-  <si>
-    <t>NEXTAR PINEAPPLE 8'S</t>
-  </si>
-  <si>
-    <t>20138465</t>
-  </si>
-  <si>
-    <t>NEXTAR STRAWBRY 90G</t>
-  </si>
-  <si>
-    <t>20124895</t>
-  </si>
-  <si>
-    <t>G/T COKIES CHOCDIP71</t>
-  </si>
-  <si>
-    <t>10003324</t>
-  </si>
-  <si>
-    <t>MONDE GENJIE PIE 70G</t>
-  </si>
-  <si>
-    <t>10008579</t>
-  </si>
-  <si>
-    <t>DELFI MINIS BLK.VN70</t>
-  </si>
-  <si>
-    <t>10008580</t>
-  </si>
-  <si>
-    <t>DELFI MINIS CHOCO 70</t>
+    <t>20135539</t>
+  </si>
+  <si>
+    <t>MR.POTATO ORGINAL85G</t>
+  </si>
+  <si>
+    <t>20136007</t>
+  </si>
+  <si>
+    <t>MR.POTATO BBQ 85G</t>
+  </si>
+  <si>
+    <t>20111009</t>
+  </si>
+  <si>
+    <t>PRINGLES CHSY CHS 42</t>
+  </si>
+  <si>
+    <t>20052859</t>
+  </si>
+  <si>
+    <t>PRINGLES ORIGINAL 42</t>
+  </si>
+  <si>
+    <t>20130007</t>
+  </si>
+  <si>
+    <t>BETTER FUN BITES 10S</t>
+  </si>
+  <si>
+    <t>20130350</t>
+  </si>
+  <si>
+    <t>POCKY CHOCOLATE 154</t>
   </si>
 </sst>
 </file>
@@ -598,7 +583,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -685,35 +670,35 @@
         <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="F5" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -722,18 +707,18 @@
         <v>8</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -742,18 +727,18 @@
         <v>8</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -762,78 +747,78 @@
         <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="F10" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>32</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -842,18 +827,18 @@
         <v>11</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
@@ -862,270 +847,250 @@
         <v>11</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>32</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/E/EG1B.xlsx
+++ b/E/EG1B.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="66">
   <si>
     <t/>
   </si>
   <si>
-    <t>20138236</t>
-  </si>
-  <si>
-    <t>CHEETOS JGG BKR 120G</t>
+    <t>10000652</t>
+  </si>
+  <si>
+    <t>INDOMI AYAM BWNG 69G</t>
   </si>
   <si>
     <t>EG1B</t>
@@ -28,169 +28,187 @@
     <t>1</t>
   </si>
   <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>10002560</t>
+  </si>
+  <si>
+    <t>INDOMI SOTO MIE 70GR</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>20137101</t>
+  </si>
+  <si>
+    <t>INDOMIE SOTO PD.D 76</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>10023789</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE GORENG 91</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20138241</t>
-  </si>
-  <si>
-    <t>CHEETOS KEJU 120G</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>20138231</t>
-  </si>
-  <si>
-    <t>DORITOS SMB SALSA120</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>20139538</t>
-  </si>
-  <si>
-    <t>LAYS RMPT LAUT 105G</t>
-  </si>
-  <si>
-    <t>20071780</t>
-  </si>
-  <si>
-    <t>POTABEE CHIP BBQ 65G</t>
+    <t>20096781</t>
+  </si>
+  <si>
+    <t>SEDAAP MI KR.SPCY 87</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>20045610</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE STO CUP81</t>
+  </si>
+  <si>
+    <t>20135720</t>
+  </si>
+  <si>
+    <t>SDP MI KARI MRCON79G</t>
+  </si>
+  <si>
+    <t>20104077</t>
+  </si>
+  <si>
+    <t>SEDAP KCP SPCL 725G</t>
+  </si>
+  <si>
+    <t>20123088</t>
+  </si>
+  <si>
+    <t>SEDAAP KCP MNS 720ML</t>
+  </si>
+  <si>
+    <t>20138950</t>
+  </si>
+  <si>
+    <t>IDM ABON AYAM 80G</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20063027</t>
+  </si>
+  <si>
+    <t>ABC SMBL EXT.PDS 270</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>20064412</t>
+  </si>
+  <si>
+    <t>ABC SAMBAL ASLI 270</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>20055205</t>
+  </si>
+  <si>
+    <t>TARO SEAWEED 62G</t>
+  </si>
+  <si>
+    <t>20055204</t>
+  </si>
+  <si>
+    <t>TARO POTATO BBQ 62G</t>
+  </si>
+  <si>
+    <t>20072575</t>
+  </si>
+  <si>
+    <t>KRISBEE F.FRIES 65G</t>
   </si>
   <si>
     <t>RT,(E-0.5B)</t>
   </si>
   <si>
-    <t>20071781</t>
-  </si>
-  <si>
-    <t>POTABEE CHIP SWD 65G</t>
-  </si>
-  <si>
-    <t>20057730</t>
-  </si>
-  <si>
-    <t>TIC TIC STCK BWNG 70</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>10000348</t>
-  </si>
-  <si>
-    <t>DK KACANG 180G</t>
-  </si>
-  <si>
-    <t>10026501</t>
-  </si>
-  <si>
-    <t>DK KACANG SUKRO 95G</t>
-  </si>
-  <si>
-    <t>20084707</t>
-  </si>
-  <si>
-    <t>SUKRO KC OVEN BWG 95</t>
-  </si>
-  <si>
-    <t>20056958</t>
-  </si>
-  <si>
-    <t>QTELA TEMPE R/LAUT55</t>
-  </si>
-  <si>
-    <t>RT,(E-14H)</t>
-  </si>
-  <si>
-    <t>20132871</t>
-  </si>
-  <si>
-    <t>DK RONI RS.CORN 135G</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>20020018</t>
-  </si>
-  <si>
-    <t>HATARI S.H.PUFF 245G</t>
+    <t>20002987</t>
+  </si>
+  <si>
+    <t>KUSUKA KRP BARBQU 60</t>
+  </si>
+  <si>
+    <t>10026500</t>
+  </si>
+  <si>
+    <t>DK KCNG BWNG PTH 180</t>
+  </si>
+  <si>
+    <t>20139132</t>
+  </si>
+  <si>
+    <t>GRUDA RS.MAX B&amp;S 80G</t>
+  </si>
+  <si>
+    <t>20072194</t>
+  </si>
+  <si>
+    <t>MH MAITOS S.BLDO 140</t>
   </si>
   <si>
     <t>RT,(E-3B)</t>
   </si>
   <si>
-    <t>20028585</t>
-  </si>
-  <si>
-    <t>MI GEMEZ ENAK PREM22</t>
-  </si>
-  <si>
-    <t>20045175</t>
-  </si>
-  <si>
-    <t>CHA CHA MILK CHO 20G</t>
-  </si>
-  <si>
-    <t>20001396</t>
-  </si>
-  <si>
-    <t>S/Q BITE CASHEW 30G</t>
-  </si>
-  <si>
-    <t>10004502</t>
-  </si>
-  <si>
-    <t>CC BIG BABOL T.FRT20</t>
-  </si>
-  <si>
-    <t>20065180</t>
-  </si>
-  <si>
-    <t>GLICO PEJOY CHO 30G</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20135539</t>
-  </si>
-  <si>
-    <t>MR.POTATO ORGINAL85G</t>
-  </si>
-  <si>
-    <t>20136007</t>
-  </si>
-  <si>
-    <t>MR.POTATO BBQ 85G</t>
-  </si>
-  <si>
-    <t>20111009</t>
-  </si>
-  <si>
-    <t>PRINGLES CHSY CHS 42</t>
-  </si>
-  <si>
-    <t>20052859</t>
-  </si>
-  <si>
-    <t>PRINGLES ORIGINAL 42</t>
-  </si>
-  <si>
-    <t>20130007</t>
-  </si>
-  <si>
-    <t>BETTER FUN BITES 10S</t>
-  </si>
-  <si>
-    <t>20130350</t>
-  </si>
-  <si>
-    <t>POCKY CHOCOLATE 154</t>
+    <t>20072195</t>
+  </si>
+  <si>
+    <t>MH MAITOS JG.BBQ 140</t>
+  </si>
+  <si>
+    <t>20097777</t>
+  </si>
+  <si>
+    <t>KRISBEE PLW CHO 100G</t>
+  </si>
+  <si>
+    <t>20130159</t>
+  </si>
+  <si>
+    <t>CADBURY SHAREBAG 81G</t>
+  </si>
+  <si>
+    <t>20048791</t>
+  </si>
+  <si>
+    <t>OREO MINI VANLA 58.4</t>
+  </si>
+  <si>
+    <t>20048790</t>
+  </si>
+  <si>
+    <t>OREO MINI CHOCO 58.4</t>
+  </si>
+  <si>
+    <t>20126401</t>
+  </si>
+  <si>
+    <t>KOKOLA KKS VANLA 218</t>
+  </si>
+  <si>
+    <t>20127761</t>
+  </si>
+  <si>
+    <t>CHCLATOS WFR CHO 90</t>
   </si>
 </sst>
 </file>
@@ -583,7 +601,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -684,41 +702,41 @@
         <v>3</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -727,18 +745,18 @@
         <v>8</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -747,107 +765,107 @@
         <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F9" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>5</v>
@@ -855,36 +873,36 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>8</v>
@@ -895,39 +913,39 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>5</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>5</v>
@@ -935,162 +953,202 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>5</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>5</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="F25" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F26" s="1" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/E/EG1B.xlsx
+++ b/E/EG1B.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="64">
   <si>
     <t/>
   </si>
   <si>
-    <t>10000652</t>
-  </si>
-  <si>
-    <t>INDOMI AYAM BWNG 69G</t>
+    <t>20136587</t>
+  </si>
+  <si>
+    <t>POP MI INDOMIE GR 80</t>
   </si>
   <si>
     <t>EG1B</t>
@@ -31,184 +31,178 @@
     <t>RT,(E-2B)</t>
   </si>
   <si>
-    <t>10002560</t>
-  </si>
-  <si>
-    <t>INDOMI SOTO MIE 70GR</t>
+    <t>10000975</t>
+  </si>
+  <si>
+    <t>POP MIE AYAM 75G</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>20137101</t>
-  </si>
-  <si>
-    <t>INDOMIE SOTO PD.D 76</t>
+    <t>10014292</t>
+  </si>
+  <si>
+    <t>POP MIE KRI AYM 75G</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>10023789</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE GORENG 91</t>
+    <t>10000861</t>
+  </si>
+  <si>
+    <t>POP MIE BASO 75G</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
+    <t>20127763</t>
+  </si>
+  <si>
+    <t>GAGA100 K.SOTO CUP75</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20098948</t>
+  </si>
+  <si>
+    <t>GAGA100 G.JLPN CUP75</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>20123088</t>
+  </si>
+  <si>
+    <t>SEDAAP KCP MNS 720ML</t>
+  </si>
+  <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20096781</t>
-  </si>
-  <si>
-    <t>SEDAAP MI KR.SPCY 87</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>20045610</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE STO CUP81</t>
-  </si>
-  <si>
-    <t>20135720</t>
-  </si>
-  <si>
-    <t>SDP MI KARI MRCON79G</t>
-  </si>
-  <si>
-    <t>20104077</t>
-  </si>
-  <si>
-    <t>SEDAP KCP SPCL 725G</t>
-  </si>
-  <si>
-    <t>20123088</t>
-  </si>
-  <si>
-    <t>SEDAAP KCP MNS 720ML</t>
-  </si>
-  <si>
-    <t>20138950</t>
-  </si>
-  <si>
-    <t>IDM ABON AYAM 80G</t>
+    <t>10016646</t>
+  </si>
+  <si>
+    <t>INDO/F KECAP MN.R725</t>
+  </si>
+  <si>
+    <t>10003517</t>
+  </si>
+  <si>
+    <t>INDOMI GORENG SPC 80</t>
+  </si>
+  <si>
+    <t>10000185</t>
+  </si>
+  <si>
+    <t>INDOMI KARI AYAM 72G</t>
+  </si>
+  <si>
+    <t>10023790</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE AYM BWG70</t>
+  </si>
+  <si>
+    <t>10023792</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE SOTO 76GR</t>
+  </si>
+  <si>
+    <t>20126424</t>
+  </si>
+  <si>
+    <t>TARO SEAWEED 115G</t>
+  </si>
+  <si>
+    <t>20116670</t>
+  </si>
+  <si>
+    <t>CHTATO LITE NORI 65G</t>
+  </si>
+  <si>
+    <t>RT,(E-14H)</t>
+  </si>
+  <si>
+    <t>20021032</t>
+  </si>
+  <si>
+    <t>QTELA KERIPIK BLD 60</t>
+  </si>
+  <si>
+    <t>20116410</t>
+  </si>
+  <si>
+    <t>CHIKI TWIST CORN 75G</t>
+  </si>
+  <si>
+    <t>20133506</t>
+  </si>
+  <si>
+    <t>DELFI KRICE SWET64.8</t>
+  </si>
+  <si>
+    <t>20048791</t>
+  </si>
+  <si>
+    <t>OREO MINI VANLA 58.4</t>
+  </si>
+  <si>
+    <t>20048790</t>
+  </si>
+  <si>
+    <t>OREO MINI CHOCO 58.4</t>
+  </si>
+  <si>
+    <t>10008579</t>
+  </si>
+  <si>
+    <t>DELFI MINIS BLK.VN70</t>
+  </si>
+  <si>
+    <t>20138332</t>
+  </si>
+  <si>
+    <t>CHOCOLATOS RICH 54G</t>
+  </si>
+  <si>
+    <t>20129961</t>
+  </si>
+  <si>
+    <t>MR.POTATO ORG KLG 35</t>
+  </si>
+  <si>
+    <t>20118290</t>
+  </si>
+  <si>
+    <t>PTNE BIOTIN S COND70</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20134589</t>
+  </si>
+  <si>
+    <t>PANTENE SHP HFC 110</t>
+  </si>
+  <si>
+    <t>20141324</t>
+  </si>
+  <si>
+    <t>DOWNY SUNSHINE 500ML</t>
   </si>
   <si>
     <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20063027</t>
-  </si>
-  <si>
-    <t>ABC SMBL EXT.PDS 270</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20064412</t>
-  </si>
-  <si>
-    <t>ABC SAMBAL ASLI 270</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>20055205</t>
-  </si>
-  <si>
-    <t>TARO SEAWEED 62G</t>
-  </si>
-  <si>
-    <t>20055204</t>
-  </si>
-  <si>
-    <t>TARO POTATO BBQ 62G</t>
-  </si>
-  <si>
-    <t>20072575</t>
-  </si>
-  <si>
-    <t>KRISBEE F.FRIES 65G</t>
-  </si>
-  <si>
-    <t>RT,(E-0.5B)</t>
-  </si>
-  <si>
-    <t>20002987</t>
-  </si>
-  <si>
-    <t>KUSUKA KRP BARBQU 60</t>
-  </si>
-  <si>
-    <t>10026500</t>
-  </si>
-  <si>
-    <t>DK KCNG BWNG PTH 180</t>
-  </si>
-  <si>
-    <t>20139132</t>
-  </si>
-  <si>
-    <t>GRUDA RS.MAX B&amp;S 80G</t>
-  </si>
-  <si>
-    <t>20072194</t>
-  </si>
-  <si>
-    <t>MH MAITOS S.BLDO 140</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20072195</t>
-  </si>
-  <si>
-    <t>MH MAITOS JG.BBQ 140</t>
-  </si>
-  <si>
-    <t>20097777</t>
-  </si>
-  <si>
-    <t>KRISBEE PLW CHO 100G</t>
-  </si>
-  <si>
-    <t>20130159</t>
-  </si>
-  <si>
-    <t>CADBURY SHAREBAG 81G</t>
-  </si>
-  <si>
-    <t>20048791</t>
-  </si>
-  <si>
-    <t>OREO MINI VANLA 58.4</t>
-  </si>
-  <si>
-    <t>20048790</t>
-  </si>
-  <si>
-    <t>OREO MINI CHOCO 58.4</t>
-  </si>
-  <si>
-    <t>20126401</t>
-  </si>
-  <si>
-    <t>KOKOLA KKS VANLA 218</t>
-  </si>
-  <si>
-    <t>20127761</t>
-  </si>
-  <si>
-    <t>CHCLATOS WFR CHO 90</t>
   </si>
 </sst>
 </file>
@@ -601,14 +595,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -708,15 +702,15 @@
         <v>14</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -725,10 +719,10 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -742,21 +736,21 @@
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -765,18 +759,18 @@
         <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -785,18 +779,18 @@
         <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -805,18 +799,18 @@
         <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -825,18 +819,18 @@
         <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -845,10 +839,10 @@
         <v>8</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -865,18 +859,18 @@
         <v>8</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
@@ -893,10 +887,10 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
@@ -908,7 +902,7 @@
         <v>8</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -928,15 +922,15 @@
         <v>11</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>44</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
@@ -948,15 +942,15 @@
         <v>14</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
@@ -968,15 +962,15 @@
         <v>4</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>48</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
@@ -988,15 +982,15 @@
         <v>8</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>50</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
@@ -1008,15 +1002,15 @@
         <v>11</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>51</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
@@ -1028,15 +1022,15 @@
         <v>14</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>51</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
@@ -1045,110 +1039,90 @@
         <v>14</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F24" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>61</v>
-      </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>15</v>
+        <v>58</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="C26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/E/EG1B.xlsx
+++ b/E/EG1B.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="66">
   <si>
     <t/>
   </si>
@@ -181,28 +181,34 @@
     <t>MR.POTATO ORG KLG 35</t>
   </si>
   <si>
-    <t>20118290</t>
-  </si>
-  <si>
-    <t>PTNE BIOTIN S COND70</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20134589</t>
-  </si>
-  <si>
-    <t>PANTENE SHP HFC 110</t>
-  </si>
-  <si>
-    <t>20141324</t>
-  </si>
-  <si>
-    <t>DOWNY SUNSHINE 500ML</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
+    <t>20049190</t>
+  </si>
+  <si>
+    <t>GERY MLKS SLT COK100</t>
+  </si>
+  <si>
+    <t>20139061</t>
+  </si>
+  <si>
+    <t>BISKUAT BITE CKLT 35</t>
+  </si>
+  <si>
+    <t>20139060</t>
+  </si>
+  <si>
+    <t>BISKUAT BITE ORI 35G</t>
+  </si>
+  <si>
+    <t>20124895</t>
+  </si>
+  <si>
+    <t>G/T COKIES CHOCDIP71</t>
+  </si>
+  <si>
+    <t>20020017</t>
+  </si>
+  <si>
+    <t>A.T.B MARIE SUSU 180</t>
   </si>
 </sst>
 </file>
@@ -595,7 +601,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1082,15 +1088,15 @@
         <v>4</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>60</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
@@ -1102,15 +1108,15 @@
         <v>8</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>62</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
@@ -1122,7 +1128,47 @@
         <v>11</v>
       </c>
       <c r="F26" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>63</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/E/EG1B.xlsx
+++ b/E/EG1B.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="67">
   <si>
     <t/>
   </si>
   <si>
-    <t>20136587</t>
-  </si>
-  <si>
-    <t>POP MI INDOMIE GR 80</t>
+    <t>10036957</t>
+  </si>
+  <si>
+    <t>HAPPYTOS CHIP HJU140</t>
   </si>
   <si>
     <t>EG1B</t>
@@ -31,184 +31,187 @@
     <t>RT,(E-2B)</t>
   </si>
   <si>
-    <t>10000975</t>
-  </si>
-  <si>
-    <t>POP MIE AYAM 75G</t>
+    <t>20098166</t>
+  </si>
+  <si>
+    <t>HAPPYTOS JG.BKR 140</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>10014292</t>
-  </si>
-  <si>
-    <t>POP MIE KRI AYM 75G</t>
+    <t>20138230</t>
+  </si>
+  <si>
+    <t>DORITOS JGG BKR 120G</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>10000861</t>
-  </si>
-  <si>
-    <t>POP MIE BASO 75G</t>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20138231</t>
+  </si>
+  <si>
+    <t>DORITOS SMB SALSA120</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>20127763</t>
-  </si>
-  <si>
-    <t>GAGA100 K.SOTO CUP75</t>
+    <t>20140882</t>
+  </si>
+  <si>
+    <t>LAYS WAVY SAPI 105G</t>
+  </si>
+  <si>
+    <t>20139538</t>
+  </si>
+  <si>
+    <t>LAYS RMPT LAUT 105G</t>
+  </si>
+  <si>
+    <t>20138228</t>
+  </si>
+  <si>
+    <t>LAYS RUMPUT LAUT 64G</t>
+  </si>
+  <si>
+    <t>20138229</t>
+  </si>
+  <si>
+    <t>LAYS DGG SAPI BKR64G</t>
+  </si>
+  <si>
+    <t>10000753</t>
+  </si>
+  <si>
+    <t>TARO SNACK SEAWED 32</t>
+  </si>
+  <si>
+    <t>10000752</t>
+  </si>
+  <si>
+    <t>TARO SNACK BARBQ 32G</t>
+  </si>
+  <si>
+    <t>20023148</t>
+  </si>
+  <si>
+    <t>TIC TAC SAPI PNGG 80</t>
+  </si>
+  <si>
+    <t>20040528</t>
+  </si>
+  <si>
+    <t>TIC TAC MIX 80G</t>
+  </si>
+  <si>
+    <t>10006534</t>
+  </si>
+  <si>
+    <t>YUPI GUMMY KS.STW 45</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20098948</t>
-  </si>
-  <si>
-    <t>GAGA100 G.JLPN CUP75</t>
+    <t>10000175</t>
+  </si>
+  <si>
+    <t>NISSIN WFR CHO 110G</t>
+  </si>
+  <si>
+    <t>20138261</t>
+  </si>
+  <si>
+    <t>POCKY BLUEBERRY 38G</t>
+  </si>
+  <si>
+    <t>20134839</t>
+  </si>
+  <si>
+    <t>POCKY CRSHD DRK.CH25</t>
+  </si>
+  <si>
+    <t>10000213</t>
+  </si>
+  <si>
+    <t>GLICO POCKY CHO 47GR</t>
+  </si>
+  <si>
+    <t>10036916</t>
+  </si>
+  <si>
+    <t>GLICO POCKY.STRAW 45</t>
+  </si>
+  <si>
+    <t>20062839</t>
+  </si>
+  <si>
+    <t>GLCO POCKY MTCHA 33G</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>20123088</t>
-  </si>
-  <si>
-    <t>SEDAAP KCP MNS 720ML</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>10016646</t>
-  </si>
-  <si>
-    <t>INDO/F KECAP MN.R725</t>
-  </si>
-  <si>
-    <t>10003517</t>
-  </si>
-  <si>
-    <t>INDOMI GORENG SPC 80</t>
-  </si>
-  <si>
-    <t>10000185</t>
-  </si>
-  <si>
-    <t>INDOMI KARI AYAM 72G</t>
-  </si>
-  <si>
-    <t>10023790</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE AYM BWG70</t>
-  </si>
-  <si>
-    <t>10023792</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE SOTO 76GR</t>
-  </si>
-  <si>
-    <t>20126424</t>
-  </si>
-  <si>
-    <t>TARO SEAWEED 115G</t>
-  </si>
-  <si>
-    <t>20116670</t>
-  </si>
-  <si>
-    <t>CHTATO LITE NORI 65G</t>
-  </si>
-  <si>
-    <t>RT,(E-14H)</t>
-  </si>
-  <si>
-    <t>20021032</t>
-  </si>
-  <si>
-    <t>QTELA KERIPIK BLD 60</t>
-  </si>
-  <si>
-    <t>20116410</t>
-  </si>
-  <si>
-    <t>CHIKI TWIST CORN 75G</t>
-  </si>
-  <si>
-    <t>20133506</t>
-  </si>
-  <si>
-    <t>DELFI KRICE SWET64.8</t>
-  </si>
-  <si>
-    <t>20048791</t>
-  </si>
-  <si>
-    <t>OREO MINI VANLA 58.4</t>
-  </si>
-  <si>
-    <t>20048790</t>
-  </si>
-  <si>
-    <t>OREO MINI CHOCO 58.4</t>
-  </si>
-  <si>
-    <t>10008579</t>
-  </si>
-  <si>
-    <t>DELFI MINIS BLK.VN70</t>
-  </si>
-  <si>
-    <t>20138332</t>
-  </si>
-  <si>
-    <t>CHOCOLATOS RICH 54G</t>
-  </si>
-  <si>
-    <t>20129961</t>
-  </si>
-  <si>
-    <t>MR.POTATO ORG KLG 35</t>
-  </si>
-  <si>
-    <t>20049190</t>
-  </si>
-  <si>
-    <t>GERY MLKS SLT COK100</t>
-  </si>
-  <si>
-    <t>20139061</t>
-  </si>
-  <si>
-    <t>BISKUAT BITE CKLT 35</t>
-  </si>
-  <si>
-    <t>20139060</t>
-  </si>
-  <si>
-    <t>BISKUAT BITE ORI 35G</t>
-  </si>
-  <si>
-    <t>20124895</t>
-  </si>
-  <si>
-    <t>G/T COKIES CHOCDIP71</t>
-  </si>
-  <si>
-    <t>20020017</t>
-  </si>
-  <si>
-    <t>A.T.B MARIE SUSU 180</t>
+    <t>20141457</t>
+  </si>
+  <si>
+    <t>PRLGS BR SWD 102</t>
+  </si>
+  <si>
+    <t>RT,(E-27H)</t>
+  </si>
+  <si>
+    <t>20135539</t>
+  </si>
+  <si>
+    <t>MR.POTATO ORGINAL85G</t>
+  </si>
+  <si>
+    <t>20136007</t>
+  </si>
+  <si>
+    <t>MR.POTATO BBQ 85G</t>
+  </si>
+  <si>
+    <t>20135538</t>
+  </si>
+  <si>
+    <t>MR.POTATO SOUR&amp;O 85G</t>
+  </si>
+  <si>
+    <t>20139392</t>
+  </si>
+  <si>
+    <t>BRINGZ LMIER BTR 100</t>
+  </si>
+  <si>
+    <t>20137570</t>
+  </si>
+  <si>
+    <t>NABATI BIG RL CHS48G</t>
+  </si>
+  <si>
+    <t>20138461</t>
+  </si>
+  <si>
+    <t>NABATI ROLL STRAW 55</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>20039717</t>
+  </si>
+  <si>
+    <t>CADBURY DAIRY MLK 52</t>
+  </si>
+  <si>
+    <t>8</t>
   </si>
 </sst>
 </file>
@@ -688,15 +691,15 @@
         <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -705,58 +708,58 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="F6" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -765,18 +768,18 @@
         <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -785,27 +788,27 @@
         <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>5</v>
@@ -813,19 +816,19 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>5</v>
@@ -833,50 +836,50 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
@@ -885,270 +888,270 @@
         <v>11</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E17" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="F17" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>50</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>57</v>
-      </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>59</v>
-      </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>61</v>
-      </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="C27" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E27" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C27" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="F27" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1162,13 +1165,13 @@
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>17</v>
+        <v>66</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/E/EG1B.xlsx
+++ b/E/EG1B.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="67">
   <si>
     <t/>
   </si>
   <si>
-    <t>10036957</t>
-  </si>
-  <si>
-    <t>HAPPYTOS CHIP HJU140</t>
+    <t>20000516</t>
+  </si>
+  <si>
+    <t>KUSUKA KRPK BBQ 180</t>
   </si>
   <si>
     <t>EG1B</t>
@@ -31,187 +31,187 @@
     <t>RT,(E-2B)</t>
   </si>
   <si>
-    <t>20098166</t>
-  </si>
-  <si>
-    <t>HAPPYTOS JG.BKR 140</t>
+    <t>20099955</t>
+  </si>
+  <si>
+    <t>PANCHOS SAPI.PG 140G</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>20138230</t>
-  </si>
-  <si>
-    <t>DORITOS JGG BKR 120G</t>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20072194</t>
+  </si>
+  <si>
+    <t>MH MAITOS S.BLDO 140</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20138231</t>
-  </si>
-  <si>
-    <t>DORITOS SMB SALSA120</t>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>10003381</t>
+  </si>
+  <si>
+    <t>GARUDA KC.GARING 160</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>20140882</t>
-  </si>
-  <si>
-    <t>LAYS WAVY SAPI 105G</t>
-  </si>
-  <si>
-    <t>20139538</t>
-  </si>
-  <si>
-    <t>LAYS RMPT LAUT 105G</t>
-  </si>
-  <si>
-    <t>20138228</t>
-  </si>
-  <si>
-    <t>LAYS RUMPUT LAUT 64G</t>
-  </si>
-  <si>
-    <t>20138229</t>
-  </si>
-  <si>
-    <t>LAYS DGG SAPI BKR64G</t>
-  </si>
-  <si>
-    <t>10000753</t>
-  </si>
-  <si>
-    <t>TARO SNACK SEAWED 32</t>
-  </si>
-  <si>
-    <t>10000752</t>
-  </si>
-  <si>
-    <t>TARO SNACK BARBQ 32G</t>
-  </si>
-  <si>
-    <t>20023148</t>
-  </si>
-  <si>
-    <t>TIC TAC SAPI PNGG 80</t>
-  </si>
-  <si>
-    <t>20040528</t>
-  </si>
-  <si>
-    <t>TIC TAC MIX 80G</t>
-  </si>
-  <si>
-    <t>10006534</t>
-  </si>
-  <si>
-    <t>YUPI GUMMY KS.STW 45</t>
+    <t>20138236</t>
+  </si>
+  <si>
+    <t>CHEETOS JGG BKR 120G</t>
+  </si>
+  <si>
+    <t>20116670</t>
+  </si>
+  <si>
+    <t>CHTATO LITE NORI 65G</t>
+  </si>
+  <si>
+    <t>RT,(E-14H)</t>
+  </si>
+  <si>
+    <t>20012679</t>
+  </si>
+  <si>
+    <t>QTELA KRIPIK BBQ 60</t>
+  </si>
+  <si>
+    <t>20116411</t>
+  </si>
+  <si>
+    <t>CHIKI PUFFS CHSE 60G</t>
+  </si>
+  <si>
+    <t>20104728</t>
+  </si>
+  <si>
+    <t>CHIMI KRP.UB JG.BK41</t>
+  </si>
+  <si>
+    <t>20131047</t>
+  </si>
+  <si>
+    <t>CHIMI KR.MENTEGA 41</t>
+  </si>
+  <si>
+    <t>10006890</t>
+  </si>
+  <si>
+    <t>TWISTKO JGNG BKR 40G</t>
+  </si>
+  <si>
+    <t>20056977</t>
+  </si>
+  <si>
+    <t>GARUDA ROSTA BWG 95</t>
+  </si>
+  <si>
+    <t>20072575</t>
+  </si>
+  <si>
+    <t>KRISBEE F.FRIES 65G</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>10000175</t>
-  </si>
-  <si>
-    <t>NISSIN WFR CHO 110G</t>
-  </si>
-  <si>
-    <t>20138261</t>
-  </si>
-  <si>
-    <t>POCKY BLUEBERRY 38G</t>
-  </si>
-  <si>
-    <t>20134839</t>
-  </si>
-  <si>
-    <t>POCKY CRSHD DRK.CH25</t>
-  </si>
-  <si>
-    <t>10000213</t>
-  </si>
-  <si>
-    <t>GLICO POCKY CHO 47GR</t>
-  </si>
-  <si>
-    <t>10036916</t>
-  </si>
-  <si>
-    <t>GLICO POCKY.STRAW 45</t>
-  </si>
-  <si>
-    <t>20062839</t>
-  </si>
-  <si>
-    <t>GLCO POCKY MTCHA 33G</t>
+    <t>RT,(E-0.5B)</t>
+  </si>
+  <si>
+    <t>10003507</t>
+  </si>
+  <si>
+    <t>MR.P KACANG MADU 80G</t>
+  </si>
+  <si>
+    <t>20115505</t>
+  </si>
+  <si>
+    <t>DILAN CHOCO CRML 95G</t>
+  </si>
+  <si>
+    <t>20102638</t>
+  </si>
+  <si>
+    <t>DEKA WFR BITE CHO 72</t>
+  </si>
+  <si>
+    <t>20134691</t>
+  </si>
+  <si>
+    <t>TWB CRACKR RAINBOW57</t>
+  </si>
+  <si>
+    <t>RT,(E-1.5B)</t>
+  </si>
+  <si>
+    <t>20130152</t>
+  </si>
+  <si>
+    <t>LEMONILO BROWNIES 33</t>
+  </si>
+  <si>
+    <t>20132494</t>
+  </si>
+  <si>
+    <t>LEMONILO BRWNS KJU33</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>20141457</t>
-  </si>
-  <si>
-    <t>PRLGS BR SWD 102</t>
-  </si>
-  <si>
-    <t>RT,(E-27H)</t>
-  </si>
-  <si>
-    <t>20135539</t>
-  </si>
-  <si>
-    <t>MR.POTATO ORGINAL85G</t>
-  </si>
-  <si>
-    <t>20136007</t>
-  </si>
-  <si>
-    <t>MR.POTATO BBQ 85G</t>
-  </si>
-  <si>
-    <t>20135538</t>
-  </si>
-  <si>
-    <t>MR.POTATO SOUR&amp;O 85G</t>
-  </si>
-  <si>
-    <t>20139392</t>
-  </si>
-  <si>
-    <t>BRINGZ LMIER BTR 100</t>
-  </si>
-  <si>
-    <t>20137570</t>
-  </si>
-  <si>
-    <t>NABATI BIG RL CHS48G</t>
-  </si>
-  <si>
-    <t>20138461</t>
-  </si>
-  <si>
-    <t>NABATI ROLL STRAW 55</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>20039717</t>
-  </si>
-  <si>
-    <t>CADBURY DAIRY MLK 52</t>
-  </si>
-  <si>
-    <t>8</t>
+    <t>20140418</t>
+  </si>
+  <si>
+    <t>SOFTX GRVTY 23CM 20S</t>
+  </si>
+  <si>
+    <t>RT</t>
+  </si>
+  <si>
+    <t>20038185</t>
+  </si>
+  <si>
+    <t>SOFTEX PL DS NP 44'S</t>
+  </si>
+  <si>
+    <t>20133708</t>
+  </si>
+  <si>
+    <t>SFTEX PW CMF/NGHT18S</t>
+  </si>
+  <si>
+    <t>20091326</t>
+  </si>
+  <si>
+    <t>PLOSSA P&amp;S ECALYPT10</t>
+  </si>
+  <si>
+    <t>20041621</t>
+  </si>
+  <si>
+    <t>ANTANGIN JRG 5X15ML</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20128440</t>
+  </si>
+  <si>
+    <t>SALONPAS EX.HOT 5X2S</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
   </si>
 </sst>
 </file>
@@ -604,14 +604,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -671,15 +671,15 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -688,18 +688,18 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -708,18 +708,18 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -731,15 +731,15 @@
         <v>4</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -751,15 +751,15 @@
         <v>8</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -768,18 +768,18 @@
         <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -788,390 +788,350 @@
         <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>12</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>12</v>
+        <v>63</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E28" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/E/EG1B.xlsx
+++ b/E/EG1B.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="62">
   <si>
     <t/>
   </si>
@@ -169,49 +169,34 @@
     <t>6</t>
   </si>
   <si>
-    <t>20140418</t>
-  </si>
-  <si>
-    <t>SOFTX GRVTY 23CM 20S</t>
-  </si>
-  <si>
-    <t>RT</t>
-  </si>
-  <si>
-    <t>20038185</t>
-  </si>
-  <si>
-    <t>SOFTEX PL DS NP 44'S</t>
-  </si>
-  <si>
-    <t>20133708</t>
-  </si>
-  <si>
-    <t>SFTEX PW CMF/NGHT18S</t>
-  </si>
-  <si>
-    <t>20091326</t>
-  </si>
-  <si>
-    <t>PLOSSA P&amp;S ECALYPT10</t>
-  </si>
-  <si>
-    <t>20041621</t>
-  </si>
-  <si>
-    <t>ANTANGIN JRG 5X15ML</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20128440</t>
-  </si>
-  <si>
-    <t>SALONPAS EX.HOT 5X2S</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
+    <t>20063488</t>
+  </si>
+  <si>
+    <t>ROMA ARDEN CHOCO 72G</t>
+  </si>
+  <si>
+    <t>20141002</t>
+  </si>
+  <si>
+    <t>WONHAE MTCHA BRY 30G</t>
+  </si>
+  <si>
+    <t>20140013</t>
+  </si>
+  <si>
+    <t>M&amp;M'S CHOC CRSPY 30G</t>
+  </si>
+  <si>
+    <t>10035165</t>
+  </si>
+  <si>
+    <t>OREO ORIGINAL 105G</t>
+  </si>
+  <si>
+    <t>20134983</t>
+  </si>
+  <si>
+    <t>RITZ CRCKRS CHSE 91G</t>
   </si>
 </sst>
 </file>
@@ -604,7 +589,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1031,15 +1016,15 @@
         <v>4</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>54</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
@@ -1051,15 +1036,15 @@
         <v>8</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>54</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>57</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>58</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
@@ -1071,15 +1056,15 @@
         <v>12</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>60</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
@@ -1091,15 +1076,15 @@
         <v>16</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>62</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
@@ -1111,27 +1096,7 @@
         <v>36</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>66</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/E/EG1B.xlsx
+++ b/E/EG1B.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="63">
   <si>
     <t/>
   </si>
   <si>
-    <t>20000516</t>
-  </si>
-  <si>
-    <t>KUSUKA KRPK BBQ 180</t>
+    <t>20130447</t>
+  </si>
+  <si>
+    <t>TOS TOS TRTCS RC140</t>
   </si>
   <si>
     <t>EG1B</t>
@@ -28,175 +28,178 @@
     <t>1</t>
   </si>
   <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20128517</t>
+  </si>
+  <si>
+    <t>TOS TOS TRTCS KB140</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>20137778</t>
+  </si>
+  <si>
+    <t>CHIMI JG.BKR 85G</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>10026500</t>
+  </si>
+  <si>
+    <t>DK KCNG BWNG PTH 180</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>20141100</t>
+  </si>
+  <si>
+    <t>WONHAE BANANA MB 60G</t>
+  </si>
+  <si>
+    <t>10026501</t>
+  </si>
+  <si>
+    <t>DK KACANG SUKRO 95G</t>
+  </si>
+  <si>
+    <t>20084707</t>
+  </si>
+  <si>
+    <t>SUKRO KC OVEN BWG 95</t>
+  </si>
+  <si>
+    <t>20062966</t>
+  </si>
+  <si>
+    <t>DK SUKRO BBQ 95G</t>
+  </si>
+  <si>
+    <t>20072316</t>
+  </si>
+  <si>
+    <t>D/K SUKRO KEDELE 95G</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>20139969</t>
+  </si>
+  <si>
+    <t>GERY SNAK BANTAL 75G</t>
+  </si>
+  <si>
+    <t>20137876</t>
+  </si>
+  <si>
+    <t>IDM KACANG OVEN 95G</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20137880</t>
+  </si>
+  <si>
+    <t>IDM KACANG KRIUK 95G</t>
+  </si>
+  <si>
+    <t>20047037</t>
+  </si>
+  <si>
+    <t>IDM KACANG BALI 150G</t>
+  </si>
+  <si>
+    <t>20028585</t>
+  </si>
+  <si>
+    <t>MI GEMEZ ENAK PREM22</t>
+  </si>
+  <si>
+    <t>20095220</t>
+  </si>
+  <si>
+    <t>GERY MLK COK CNUT105</t>
+  </si>
+  <si>
+    <t>20065096</t>
+  </si>
+  <si>
+    <t>GERY MLKS SLT KJU100</t>
+  </si>
+  <si>
+    <t>20127761</t>
+  </si>
+  <si>
+    <t>CHCLATOS WFR CHO 90</t>
+  </si>
+  <si>
+    <t>10034901</t>
+  </si>
+  <si>
+    <t>CHO-CHO WFR CRISPY33</t>
+  </si>
+  <si>
     <t>RT,(E-2B)</t>
   </si>
   <si>
-    <t>20099955</t>
-  </si>
-  <si>
-    <t>PANCHOS SAPI.PG 140G</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20072194</t>
-  </si>
-  <si>
-    <t>MH MAITOS S.BLDO 140</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>10003381</t>
-  </si>
-  <si>
-    <t>GARUDA KC.GARING 160</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>20138236</t>
-  </si>
-  <si>
-    <t>CHEETOS JGG BKR 120G</t>
-  </si>
-  <si>
-    <t>20116670</t>
-  </si>
-  <si>
-    <t>CHTATO LITE NORI 65G</t>
-  </si>
-  <si>
-    <t>RT,(E-14H)</t>
-  </si>
-  <si>
-    <t>20012679</t>
-  </si>
-  <si>
-    <t>QTELA KRIPIK BBQ 60</t>
-  </si>
-  <si>
-    <t>20116411</t>
-  </si>
-  <si>
-    <t>CHIKI PUFFS CHSE 60G</t>
-  </si>
-  <si>
-    <t>20104728</t>
-  </si>
-  <si>
-    <t>CHIMI KRP.UB JG.BK41</t>
-  </si>
-  <si>
-    <t>20131047</t>
-  </si>
-  <si>
-    <t>CHIMI KR.MENTEGA 41</t>
-  </si>
-  <si>
-    <t>10006890</t>
-  </si>
-  <si>
-    <t>TWISTKO JGNG BKR 40G</t>
-  </si>
-  <si>
-    <t>20056977</t>
-  </si>
-  <si>
-    <t>GARUDA ROSTA BWG 95</t>
-  </si>
-  <si>
-    <t>20072575</t>
-  </si>
-  <si>
-    <t>KRISBEE F.FRIES 65G</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>RT,(E-0.5B)</t>
-  </si>
-  <si>
-    <t>10003507</t>
-  </si>
-  <si>
-    <t>MR.P KACANG MADU 80G</t>
-  </si>
-  <si>
-    <t>20115505</t>
-  </si>
-  <si>
-    <t>DILAN CHOCO CRML 95G</t>
-  </si>
-  <si>
-    <t>20102638</t>
-  </si>
-  <si>
-    <t>DEKA WFR BITE CHO 72</t>
-  </si>
-  <si>
-    <t>20134691</t>
-  </si>
-  <si>
-    <t>TWB CRACKR RAINBOW57</t>
-  </si>
-  <si>
-    <t>RT,(E-1.5B)</t>
-  </si>
-  <si>
-    <t>20130152</t>
-  </si>
-  <si>
-    <t>LEMONILO BROWNIES 33</t>
-  </si>
-  <si>
-    <t>20132494</t>
-  </si>
-  <si>
-    <t>LEMONILO BRWNS KJU33</t>
+    <t>10034899</t>
+  </si>
+  <si>
+    <t>CHO-CHO WFR STRAW 35</t>
+  </si>
+  <si>
+    <t>20139949</t>
+  </si>
+  <si>
+    <t>LMNILO CRNCHY CHO 18</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>20063488</t>
-  </si>
-  <si>
-    <t>ROMA ARDEN CHOCO 72G</t>
-  </si>
-  <si>
-    <t>20141002</t>
-  </si>
-  <si>
-    <t>WONHAE MTCHA BRY 30G</t>
-  </si>
-  <si>
-    <t>20140013</t>
-  </si>
-  <si>
-    <t>M&amp;M'S CHOC CRSPY 30G</t>
-  </si>
-  <si>
-    <t>10035165</t>
-  </si>
-  <si>
-    <t>OREO ORIGINAL 105G</t>
-  </si>
-  <si>
-    <t>20134983</t>
-  </si>
-  <si>
-    <t>RITZ CRCKRS CHSE 91G</t>
+    <t>20137583</t>
+  </si>
+  <si>
+    <t>IDM BROWNIS CHEESE35</t>
+  </si>
+  <si>
+    <t>20137584</t>
+  </si>
+  <si>
+    <t>IDM BROWNIS CHOCIP35</t>
+  </si>
+  <si>
+    <t>20137063</t>
+  </si>
+  <si>
+    <t>IDM CND GUMMY ORG88G</t>
+  </si>
+  <si>
+    <t>20125849</t>
+  </si>
+  <si>
+    <t>AMOS GUMMY 4D BLK 72</t>
+  </si>
+  <si>
+    <t>20137760</t>
+  </si>
+  <si>
+    <t>BRIO POTATO ORI 104G</t>
+  </si>
+  <si>
+    <t>20138099</t>
+  </si>
+  <si>
+    <t>OVALTINE MB WFR 100G</t>
   </si>
 </sst>
 </file>
@@ -589,14 +592,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -656,15 +659,15 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -673,18 +676,18 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -693,18 +696,18 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -716,15 +719,15 @@
         <v>4</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -736,15 +739,15 @@
         <v>8</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -753,18 +756,18 @@
         <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -773,127 +776,127 @@
         <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>35</v>
-      </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>5</v>
@@ -901,202 +904,242 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>46</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>9</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>9</v>
+        <v>45</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="C26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C25" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>9</v>
+      <c r="B27" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/E/EG1B.xlsx
+++ b/E/EG1B.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="68">
   <si>
     <t/>
   </si>
   <si>
-    <t>20130447</t>
-  </si>
-  <si>
-    <t>TOS TOS TRTCS RC140</t>
+    <t>10000975</t>
+  </si>
+  <si>
+    <t>POP MIE AYAM 75G</t>
   </si>
   <si>
     <t>EG1B</t>
@@ -28,40 +28,175 @@
     <t>1</t>
   </si>
   <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>10000861</t>
+  </si>
+  <si>
+    <t>POP MIE BASO 75G</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>20136587</t>
+  </si>
+  <si>
+    <t>POP MI INDOMIE GR 80</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>20045610</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE STO CUP81</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20128517</t>
-  </si>
-  <si>
-    <t>TOS TOS TRTCS KB140</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>20137778</t>
-  </si>
-  <si>
-    <t>CHIMI JG.BKR 85G</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>10026500</t>
-  </si>
-  <si>
-    <t>DK KCNG BWNG PTH 180</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>20141100</t>
-  </si>
-  <si>
-    <t>WONHAE BANANA MB 60G</t>
+    <t>20122255</t>
+  </si>
+  <si>
+    <t>SDP MI BASO BLDK 77G</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>20113844</t>
+  </si>
+  <si>
+    <t>SEDAAP MI AYM JRT 75</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>10023790</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE AYM BWG70</t>
+  </si>
+  <si>
+    <t>10023792</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE SOTO 76GR</t>
+  </si>
+  <si>
+    <t>20025418</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE KARI SP75</t>
+  </si>
+  <si>
+    <t>20136385</t>
+  </si>
+  <si>
+    <t>SEDAAP GRG CHF.DVN93</t>
+  </si>
+  <si>
+    <t>20096781</t>
+  </si>
+  <si>
+    <t>SEDAAP MI KR.SPCY 87</t>
+  </si>
+  <si>
+    <t>10002350</t>
+  </si>
+  <si>
+    <t>ABC KCP MANIS TGG275</t>
+  </si>
+  <si>
+    <t>20132660</t>
+  </si>
+  <si>
+    <t>2 BELIBIS SAUS 235ML</t>
+  </si>
+  <si>
+    <t>20141501</t>
+  </si>
+  <si>
+    <t>2 BELIBIS PDS LD 235</t>
+  </si>
+  <si>
+    <t>10005491</t>
+  </si>
+  <si>
+    <t>TONG TJI JASM T/A.25</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>10005073</t>
+  </si>
+  <si>
+    <t>BLUE BAND PCK 200G</t>
+  </si>
+  <si>
+    <t>20037353</t>
+  </si>
+  <si>
+    <t>SAJIKU TPG G.CRSP200</t>
+  </si>
+  <si>
+    <t>10035900</t>
+  </si>
+  <si>
+    <t>A/SAJIKU TPG SRB 210</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>20069701</t>
+  </si>
+  <si>
+    <t>MEG KEJU SRBGN 160G</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>10029542</t>
+  </si>
+  <si>
+    <t>MR.BREAD COKLAT KEJU</t>
+  </si>
+  <si>
+    <t>RT,(E-1H)</t>
+  </si>
+  <si>
+    <t>20035484</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH MLATI350</t>
+  </si>
+  <si>
+    <t>20048155</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH L/SGR350</t>
+  </si>
+  <si>
+    <t>20138252</t>
+  </si>
+  <si>
+    <t>EXTRA JOSS ULTIMT250</t>
+  </si>
+  <si>
+    <t>20132871</t>
+  </si>
+  <si>
+    <t>DK RONI RS.CORN 135G</t>
   </si>
   <si>
     <t>10026501</t>
@@ -80,126 +215,6 @@
   </si>
   <si>
     <t>DK SUKRO BBQ 95G</t>
-  </si>
-  <si>
-    <t>20072316</t>
-  </si>
-  <si>
-    <t>D/K SUKRO KEDELE 95G</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>20139969</t>
-  </si>
-  <si>
-    <t>GERY SNAK BANTAL 75G</t>
-  </si>
-  <si>
-    <t>20137876</t>
-  </si>
-  <si>
-    <t>IDM KACANG OVEN 95G</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20137880</t>
-  </si>
-  <si>
-    <t>IDM KACANG KRIUK 95G</t>
-  </si>
-  <si>
-    <t>20047037</t>
-  </si>
-  <si>
-    <t>IDM KACANG BALI 150G</t>
-  </si>
-  <si>
-    <t>20028585</t>
-  </si>
-  <si>
-    <t>MI GEMEZ ENAK PREM22</t>
-  </si>
-  <si>
-    <t>20095220</t>
-  </si>
-  <si>
-    <t>GERY MLK COK CNUT105</t>
-  </si>
-  <si>
-    <t>20065096</t>
-  </si>
-  <si>
-    <t>GERY MLKS SLT KJU100</t>
-  </si>
-  <si>
-    <t>20127761</t>
-  </si>
-  <si>
-    <t>CHCLATOS WFR CHO 90</t>
-  </si>
-  <si>
-    <t>10034901</t>
-  </si>
-  <si>
-    <t>CHO-CHO WFR CRISPY33</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>10034899</t>
-  </si>
-  <si>
-    <t>CHO-CHO WFR STRAW 35</t>
-  </si>
-  <si>
-    <t>20139949</t>
-  </si>
-  <si>
-    <t>LMNILO CRNCHY CHO 18</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20137583</t>
-  </si>
-  <si>
-    <t>IDM BROWNIS CHEESE35</t>
-  </si>
-  <si>
-    <t>20137584</t>
-  </si>
-  <si>
-    <t>IDM BROWNIS CHOCIP35</t>
-  </si>
-  <si>
-    <t>20137063</t>
-  </si>
-  <si>
-    <t>IDM CND GUMMY ORG88G</t>
-  </si>
-  <si>
-    <t>20125849</t>
-  </si>
-  <si>
-    <t>AMOS GUMMY 4D BLK 72</t>
-  </si>
-  <si>
-    <t>20137760</t>
-  </si>
-  <si>
-    <t>BRIO POTATO ORI 104G</t>
-  </si>
-  <si>
-    <t>20138099</t>
-  </si>
-  <si>
-    <t>OVALTINE MB WFR 100G</t>
   </si>
 </sst>
 </file>
@@ -592,7 +607,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -699,55 +714,55 @@
         <v>14</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -756,18 +771,18 @@
         <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -776,18 +791,18 @@
         <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -796,58 +811,58 @@
         <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
@@ -856,18 +871,18 @@
         <v>11</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
@@ -876,18 +891,18 @@
         <v>11</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
@@ -896,7 +911,7 @@
         <v>11</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>5</v>
@@ -904,110 +919,110 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F16" s="1" t="s">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>45</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>45</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
@@ -1016,130 +1031,150 @@
         <v>14</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/E/EG1B.xlsx
+++ b/E/EG1B.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="72">
   <si>
     <t/>
   </si>
@@ -166,6 +166,48 @@
     <t>8</t>
   </si>
   <si>
+    <t>20098520</t>
+  </si>
+  <si>
+    <t>IDM TISSUE PNGST 150</t>
+  </si>
+  <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20138950</t>
+  </si>
+  <si>
+    <t>IDM ABON AYAM 80G</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20093516</t>
+  </si>
+  <si>
+    <t>INDOMARET KUACI 80G</t>
+  </si>
+  <si>
+    <t>20112944</t>
+  </si>
+  <si>
+    <t>IDM KUACI SUSU 80G</t>
+  </si>
+  <si>
+    <t>20055762</t>
+  </si>
+  <si>
+    <t>JELE COLLAGEN 150G</t>
+  </si>
+  <si>
+    <t>20096795</t>
+  </si>
+  <si>
+    <t>IDM JAM STRAW 170</t>
+  </si>
+  <si>
     <t>10029542</t>
   </si>
   <si>
@@ -185,36 +227,6 @@
   </si>
   <si>
     <t>PUCUK/H TEH L/SGR350</t>
-  </si>
-  <si>
-    <t>20138252</t>
-  </si>
-  <si>
-    <t>EXTRA JOSS ULTIMT250</t>
-  </si>
-  <si>
-    <t>20132871</t>
-  </si>
-  <si>
-    <t>DK RONI RS.CORN 135G</t>
-  </si>
-  <si>
-    <t>10026501</t>
-  </si>
-  <si>
-    <t>DK KACANG SUKRO 95G</t>
-  </si>
-  <si>
-    <t>20084707</t>
-  </si>
-  <si>
-    <t>SUKRO KC OVEN BWG 95</t>
-  </si>
-  <si>
-    <t>20062966</t>
-  </si>
-  <si>
-    <t>DK SUKRO BBQ 95G</t>
   </si>
 </sst>
 </file>
@@ -607,7 +619,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1054,15 +1066,15 @@
         <v>8</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>15</v>
+        <v>56</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
@@ -1074,44 +1086,44 @@
         <v>11</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>15</v>
+        <v>56</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>15</v>
+        <v>56</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>15</v>
@@ -1119,30 +1131,30 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>15</v>
+        <v>56</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
@@ -1151,18 +1163,18 @@
         <v>18</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>15</v>
+        <v>67</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
@@ -1171,9 +1183,29 @@
         <v>18</v>
       </c>
       <c r="E28" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D29" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="E29" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F29" s="1" t="s">
         <v>15</v>
       </c>
     </row>

--- a/E/EG1B.xlsx
+++ b/E/EG1B.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="52">
   <si>
     <t/>
   </si>
   <si>
-    <t>10000975</t>
-  </si>
-  <si>
-    <t>POP MIE AYAM 75G</t>
+    <t>20124903</t>
+  </si>
+  <si>
+    <t>QTELA KR AY LD/HT100</t>
   </si>
   <si>
     <t>EG1B</t>
@@ -28,184 +28,124 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>10000861</t>
-  </si>
-  <si>
-    <t>POP MIE BASO 75G</t>
+    <t>RT,(E-14H)</t>
+  </si>
+  <si>
+    <t>20099955</t>
+  </si>
+  <si>
+    <t>PANCHOS SAPI.PG 140G</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>20136587</t>
-  </si>
-  <si>
-    <t>POP MI INDOMIE GR 80</t>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20131013</t>
+  </si>
+  <si>
+    <t>PANCHOS CABE PDS 145</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>20045610</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE STO CUP81</t>
+    <t>10000341</t>
+  </si>
+  <si>
+    <t>DUA KELINCI KCG 370G</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20122255</t>
-  </si>
-  <si>
-    <t>SDP MI BASO BLDK 77G</t>
+    <t>20071781</t>
+  </si>
+  <si>
+    <t>POTABEE CHIP SWD 65G</t>
+  </si>
+  <si>
+    <t>RT,(E-0.5B)</t>
+  </si>
+  <si>
+    <t>20114756</t>
+  </si>
+  <si>
+    <t>GURIBEE BBQ BLDO 65G</t>
+  </si>
+  <si>
+    <t>20072575</t>
+  </si>
+  <si>
+    <t>KRISBEE F.FRIES 65G</t>
+  </si>
+  <si>
+    <t>20004229</t>
+  </si>
+  <si>
+    <t>SMAX RING CHEESE 40G</t>
+  </si>
+  <si>
+    <t>20095220</t>
+  </si>
+  <si>
+    <t>GERY MLK COK CNUT105</t>
+  </si>
+  <si>
+    <t>10038628</t>
+  </si>
+  <si>
+    <t>HATARI BIS.PEANUT225</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20027448</t>
+  </si>
+  <si>
+    <t>TANGO WFR CHOC 100G</t>
+  </si>
+  <si>
+    <t>20084899</t>
+  </si>
+  <si>
+    <t>L`AGIE GLDN CITY 75G</t>
+  </si>
+  <si>
+    <t>10038704</t>
+  </si>
+  <si>
+    <t>MEIJI H/PANDA CHOC42</t>
+  </si>
+  <si>
+    <t>10004490</t>
+  </si>
+  <si>
+    <t>HELLO PANDA STRW 42G</t>
+  </si>
+  <si>
+    <t>20091350</t>
+  </si>
+  <si>
+    <t>ROMA MARIE GOLD 220G</t>
+  </si>
+  <si>
+    <t>10000103</t>
+  </si>
+  <si>
+    <t>REGAL MARIE 230GR</t>
+  </si>
+  <si>
+    <t>20130007</t>
+  </si>
+  <si>
+    <t>BETTER FUN BITES 10S</t>
   </si>
   <si>
     <t>5</t>
-  </si>
-  <si>
-    <t>20113844</t>
-  </si>
-  <si>
-    <t>SEDAAP MI AYM JRT 75</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>10023790</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE AYM BWG70</t>
-  </si>
-  <si>
-    <t>10023792</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE SOTO 76GR</t>
-  </si>
-  <si>
-    <t>20025418</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE KARI SP75</t>
-  </si>
-  <si>
-    <t>20136385</t>
-  </si>
-  <si>
-    <t>SEDAAP GRG CHF.DVN93</t>
-  </si>
-  <si>
-    <t>20096781</t>
-  </si>
-  <si>
-    <t>SEDAAP MI KR.SPCY 87</t>
-  </si>
-  <si>
-    <t>10002350</t>
-  </si>
-  <si>
-    <t>ABC KCP MANIS TGG275</t>
-  </si>
-  <si>
-    <t>20132660</t>
-  </si>
-  <si>
-    <t>2 BELIBIS SAUS 235ML</t>
-  </si>
-  <si>
-    <t>20141501</t>
-  </si>
-  <si>
-    <t>2 BELIBIS PDS LD 235</t>
-  </si>
-  <si>
-    <t>10005491</t>
-  </si>
-  <si>
-    <t>TONG TJI JASM T/A.25</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>10005073</t>
-  </si>
-  <si>
-    <t>BLUE BAND PCK 200G</t>
-  </si>
-  <si>
-    <t>20037353</t>
-  </si>
-  <si>
-    <t>SAJIKU TPG G.CRSP200</t>
-  </si>
-  <si>
-    <t>10035900</t>
-  </si>
-  <si>
-    <t>A/SAJIKU TPG SRB 210</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>20069701</t>
-  </si>
-  <si>
-    <t>MEG KEJU SRBGN 160G</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>20098520</t>
-  </si>
-  <si>
-    <t>IDM TISSUE PNGST 150</t>
-  </si>
-  <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>20138950</t>
-  </si>
-  <si>
-    <t>IDM ABON AYAM 80G</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20093516</t>
-  </si>
-  <si>
-    <t>INDOMARET KUACI 80G</t>
-  </si>
-  <si>
-    <t>20112944</t>
-  </si>
-  <si>
-    <t>IDM KUACI SUSU 80G</t>
-  </si>
-  <si>
-    <t>20055762</t>
-  </si>
-  <si>
-    <t>JELE COLLAGEN 150G</t>
-  </si>
-  <si>
-    <t>20096795</t>
-  </si>
-  <si>
-    <t>IDM JAM STRAW 170</t>
   </si>
   <si>
     <t>10029542</t>
@@ -619,14 +559,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -686,15 +626,15 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -703,18 +643,18 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -723,10 +663,10 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -740,13 +680,13 @@
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -760,21 +700,21 @@
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>23</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -783,18 +723,18 @@
         <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -803,50 +743,50 @@
         <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="C11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -860,13 +800,13 @@
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -880,13 +820,13 @@
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -900,13 +840,13 @@
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -920,13 +860,13 @@
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -940,53 +880,53 @@
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="C18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="F18" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1000,13 +940,13 @@
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="E19" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F19" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1020,193 +960,33 @@
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/E/EG1B.xlsx
+++ b/E/EG1B.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="56">
   <si>
     <t/>
   </si>
@@ -94,6 +94,12 @@
     <t>GERY MLK COK CNUT105</t>
   </si>
   <si>
+    <t>20049190</t>
+  </si>
+  <si>
+    <t>GERY MLKS SLT COK100</t>
+  </si>
+  <si>
     <t>10038628</t>
   </si>
   <si>
@@ -109,28 +115,58 @@
     <t>TANGO WFR CHOC 100G</t>
   </si>
   <si>
+    <t>10038704</t>
+  </si>
+  <si>
+    <t>MEIJI H/PANDA CHOC42</t>
+  </si>
+  <si>
+    <t>10004490</t>
+  </si>
+  <si>
+    <t>HELLO PANDA STRW 42G</t>
+  </si>
+  <si>
+    <t>20091350</t>
+  </si>
+  <si>
+    <t>ROMA MARIE GOLD 220G</t>
+  </si>
+  <si>
     <t>20084899</t>
   </si>
   <si>
     <t>L`AGIE GLDN CITY 75G</t>
   </si>
   <si>
-    <t>10038704</t>
-  </si>
-  <si>
-    <t>MEIJI H/PANDA CHOC42</t>
-  </si>
-  <si>
-    <t>10004490</t>
-  </si>
-  <si>
-    <t>HELLO PANDA STRW 42G</t>
-  </si>
-  <si>
-    <t>20091350</t>
-  </si>
-  <si>
-    <t>ROMA MARIE GOLD 220G</t>
+    <t>20069149</t>
+  </si>
+  <si>
+    <t>TANGO WFR LG VAN 100</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>10029542</t>
+  </si>
+  <si>
+    <t>MR.BREAD COKLAT KEJU</t>
+  </si>
+  <si>
+    <t>RT,(E-1H)</t>
+  </si>
+  <si>
+    <t>20035484</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH MLATI350</t>
+  </si>
+  <si>
+    <t>20048155</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH L/SGR350</t>
   </si>
   <si>
     <t>10000103</t>
@@ -143,30 +179,6 @@
   </si>
   <si>
     <t>BETTER FUN BITES 10S</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>10029542</t>
-  </si>
-  <si>
-    <t>MR.BREAD COKLAT KEJU</t>
-  </si>
-  <si>
-    <t>RT,(E-1H)</t>
-  </si>
-  <si>
-    <t>20035484</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH MLATI350</t>
-  </si>
-  <si>
-    <t>20048155</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH L/SGR350</t>
   </si>
 </sst>
 </file>
@@ -559,7 +571,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -786,15 +798,15 @@
         <v>8</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>31</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -806,7 +818,7 @@
         <v>12</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -826,7 +838,7 @@
         <v>15</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -906,7 +918,7 @@
         <v>15</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -986,6 +998,46 @@
         <v>12</v>
       </c>
       <c r="F21" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F23" s="1" t="s">
         <v>9</v>
       </c>
     </row>

--- a/E/EG1B.xlsx
+++ b/E/EG1B.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="61">
   <si>
     <t/>
   </si>
   <si>
-    <t>20124903</t>
-  </si>
-  <si>
-    <t>QTELA KR AY LD/HT100</t>
+    <t>10023792</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE SOTO 76GR</t>
   </si>
   <si>
     <t>EG1B</t>
@@ -28,157 +28,172 @@
     <t>1</t>
   </si>
   <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>10023791</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE KR.AYAM72</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>20096781</t>
+  </si>
+  <si>
+    <t>SEDAAP MI KR.SPCY 87</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>20136385</t>
+  </si>
+  <si>
+    <t>SEDAAP GRG CHF.DVN93</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>10035852</t>
+  </si>
+  <si>
+    <t>BIHUNKU GRG SPCL 60G</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>20093110</t>
+  </si>
+  <si>
+    <t>KUSUKA BALADO 180G</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20120421</t>
+  </si>
+  <si>
+    <t>TARO POTATO BBQ 115G</t>
+  </si>
+  <si>
+    <t>20116675</t>
+  </si>
+  <si>
+    <t>CHTATO LITE NORI 115</t>
+  </si>
+  <si>
     <t>RT,(E-14H)</t>
   </si>
   <si>
-    <t>20099955</t>
-  </si>
-  <si>
-    <t>PANCHOS SAPI.PG 140G</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20131013</t>
-  </si>
-  <si>
-    <t>PANCHOS CABE PDS 145</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>10000341</t>
-  </si>
-  <si>
-    <t>DUA KELINCI KCG 370G</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>20071781</t>
-  </si>
-  <si>
-    <t>POTABEE CHIP SWD 65G</t>
-  </si>
-  <si>
-    <t>RT,(E-0.5B)</t>
-  </si>
-  <si>
-    <t>20114756</t>
-  </si>
-  <si>
-    <t>GURIBEE BBQ BLDO 65G</t>
-  </si>
-  <si>
-    <t>20072575</t>
-  </si>
-  <si>
-    <t>KRISBEE F.FRIES 65G</t>
-  </si>
-  <si>
-    <t>20004229</t>
-  </si>
-  <si>
-    <t>SMAX RING CHEESE 40G</t>
-  </si>
-  <si>
-    <t>20095220</t>
-  </si>
-  <si>
-    <t>GERY MLK COK CNUT105</t>
-  </si>
-  <si>
-    <t>20049190</t>
-  </si>
-  <si>
-    <t>GERY MLKS SLT COK100</t>
-  </si>
-  <si>
-    <t>10038628</t>
-  </si>
-  <si>
-    <t>HATARI BIS.PEANUT225</t>
+    <t>20136007</t>
+  </si>
+  <si>
+    <t>MR.POTATO BBQ 85G</t>
+  </si>
+  <si>
+    <t>20135539</t>
+  </si>
+  <si>
+    <t>MR.POTATO ORGINAL85G</t>
+  </si>
+  <si>
+    <t>20013662</t>
+  </si>
+  <si>
+    <t>BISKUAT COKLAT121.6G</t>
+  </si>
+  <si>
+    <t>20014537</t>
+  </si>
+  <si>
+    <t>BISKUAT ORIGNAL121.6</t>
+  </si>
+  <si>
+    <t>20044008</t>
+  </si>
+  <si>
+    <t>BENG-BENG MAXX 32G</t>
+  </si>
+  <si>
+    <t>20135198</t>
+  </si>
+  <si>
+    <t>WONHAE YOG.GUM ORI48</t>
+  </si>
+  <si>
+    <t>20052630</t>
+  </si>
+  <si>
+    <t>LOTTE CHOCO PIE 156G</t>
+  </si>
+  <si>
+    <t>10008550</t>
+  </si>
+  <si>
+    <t>G/T CHOCHP DB.CHO 72</t>
+  </si>
+  <si>
+    <t>10000461</t>
+  </si>
+  <si>
+    <t>MONDE SERENA GOLD 50</t>
+  </si>
+  <si>
+    <t>20098348</t>
+  </si>
+  <si>
+    <t>REBO KUACI ORIGNL120</t>
+  </si>
+  <si>
+    <t>10029542</t>
+  </si>
+  <si>
+    <t>MR.BREAD COKLAT KEJU</t>
+  </si>
+  <si>
+    <t>RT,(E-1H)</t>
+  </si>
+  <si>
+    <t>20035484</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH MLATI350</t>
+  </si>
+  <si>
+    <t>20048155</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH L/SGR350</t>
+  </si>
+  <si>
+    <t>20020018</t>
+  </si>
+  <si>
+    <t>HATARI S.H.PUFF 245G</t>
   </si>
   <si>
     <t>RT,(E-3B)</t>
   </si>
   <si>
-    <t>20027448</t>
-  </si>
-  <si>
-    <t>TANGO WFR CHOC 100G</t>
-  </si>
-  <si>
-    <t>10038704</t>
-  </si>
-  <si>
-    <t>MEIJI H/PANDA CHOC42</t>
-  </si>
-  <si>
-    <t>10004490</t>
-  </si>
-  <si>
-    <t>HELLO PANDA STRW 42G</t>
-  </si>
-  <si>
-    <t>20091350</t>
-  </si>
-  <si>
-    <t>ROMA MARIE GOLD 220G</t>
-  </si>
-  <si>
-    <t>20084899</t>
-  </si>
-  <si>
-    <t>L`AGIE GLDN CITY 75G</t>
-  </si>
-  <si>
-    <t>20069149</t>
-  </si>
-  <si>
-    <t>TANGO WFR LG VAN 100</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>10029542</t>
-  </si>
-  <si>
-    <t>MR.BREAD COKLAT KEJU</t>
-  </si>
-  <si>
-    <t>RT,(E-1H)</t>
-  </si>
-  <si>
-    <t>20035484</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH MLATI350</t>
-  </si>
-  <si>
-    <t>20048155</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH L/SGR350</t>
-  </si>
-  <si>
-    <t>10000103</t>
-  </si>
-  <si>
-    <t>REGAL MARIE 230GR</t>
-  </si>
-  <si>
-    <t>20130007</t>
-  </si>
-  <si>
-    <t>BETTER FUN BITES 10S</t>
+    <t>20053216</t>
+  </si>
+  <si>
+    <t>NSIN BSC KLP IJO 280</t>
+  </si>
+  <si>
+    <t>10000418</t>
+  </si>
+  <si>
+    <t>DELFI CHIC CHOC 36G</t>
+  </si>
+  <si>
+    <t>6</t>
   </si>
 </sst>
 </file>
@@ -571,17 +586,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="6" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -600,8 +616,14 @@
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -617,11 +639,11 @@
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -637,16 +659,16 @@
       <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="H3" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -655,18 +677,18 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="B5" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -675,38 +697,38 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="B6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F6" s="1" t="s">
+      <c r="H6" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+      <c r="B7" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>20</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -715,13 +737,13 @@
         <v>8</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>21</v>
       </c>
@@ -735,13 +757,13 @@
         <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>23</v>
       </c>
@@ -755,73 +777,73 @@
         <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F10" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H12" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>32</v>
       </c>
@@ -832,16 +854,16 @@
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>34</v>
       </c>
@@ -852,16 +874,16 @@
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>36</v>
       </c>
@@ -872,16 +894,16 @@
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>38</v>
       </c>
@@ -892,16 +914,16 @@
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>40</v>
       </c>
@@ -912,16 +934,16 @@
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>42</v>
       </c>
@@ -932,113 +954,153 @@
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E18" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F18" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
+      <c r="B19" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="C19" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E19" s="1" t="s">
+      <c r="B20" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F19" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
+      <c r="H20" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B20" s="1" t="s">
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E20" s="1" t="s">
+      <c r="B21" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F20" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B21" s="1" t="s">
+      <c r="H21" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
+      <c r="B22" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="C22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
+      <c r="B23" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="C23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H23" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>9</v>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/E/EG1B.xlsx
+++ b/E/EG1B.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="53">
   <si>
     <t/>
   </si>
@@ -170,30 +170,6 @@
   </si>
   <si>
     <t>PUCUK/H TEH L/SGR350</t>
-  </si>
-  <si>
-    <t>20020018</t>
-  </si>
-  <si>
-    <t>HATARI S.H.PUFF 245G</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20053216</t>
-  </si>
-  <si>
-    <t>NSIN BSC KLP IJO 280</t>
-  </si>
-  <si>
-    <t>10000418</t>
-  </si>
-  <si>
-    <t>DELFI CHIC CHOC 36G</t>
-  </si>
-  <si>
-    <t>6</t>
   </si>
 </sst>
 </file>
@@ -586,18 +562,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -616,14 +591,8 @@
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -639,11 +608,11 @@
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -659,11 +628,11 @@
       <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F3" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -679,11 +648,11 @@
       <c r="E4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F4" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
@@ -699,11 +668,11 @@
       <c r="E5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -719,11 +688,11 @@
       <c r="E6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H6" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F6" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
@@ -739,11 +708,11 @@
       <c r="E7" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>21</v>
       </c>
@@ -759,11 +728,11 @@
       <c r="E8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="F8" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>23</v>
       </c>
@@ -779,11 +748,11 @@
       <c r="E9" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="F9" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>26</v>
       </c>
@@ -799,11 +768,11 @@
       <c r="E10" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H10" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F10" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>28</v>
       </c>
@@ -819,11 +788,11 @@
       <c r="E11" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H11" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F11" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>30</v>
       </c>
@@ -839,11 +808,11 @@
       <c r="E12" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H12" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F12" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>32</v>
       </c>
@@ -859,11 +828,11 @@
       <c r="E13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H13" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F13" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>34</v>
       </c>
@@ -879,11 +848,11 @@
       <c r="E14" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H14" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F14" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>36</v>
       </c>
@@ -899,11 +868,11 @@
       <c r="E15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H15" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F15" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>38</v>
       </c>
@@ -919,11 +888,11 @@
       <c r="E16" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H16" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F16" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>40</v>
       </c>
@@ -939,11 +908,11 @@
       <c r="E17" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H17" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F17" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>42</v>
       </c>
@@ -959,11 +928,11 @@
       <c r="E18" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H18" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F18" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>44</v>
       </c>
@@ -979,11 +948,11 @@
       <c r="E19" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H19" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F19" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>46</v>
       </c>
@@ -999,11 +968,11 @@
       <c r="E20" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H20" s="1" t="s">
+      <c r="F20" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>49</v>
       </c>
@@ -1019,11 +988,11 @@
       <c r="E21" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H21" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F21" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>51</v>
       </c>
@@ -1039,67 +1008,7 @@
       <c r="E22" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H22" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="H25" s="1" t="s">
+      <c r="F22" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/E/EG1B.xlsx
+++ b/E/EG1B.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="72">
   <si>
     <t/>
   </si>
   <si>
-    <t>10023792</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE SOTO 76GR</t>
+    <t>10000975</t>
+  </si>
+  <si>
+    <t>POP MIE AYAM 75G</t>
   </si>
   <si>
     <t>EG1B</t>
@@ -28,133 +28,163 @@
     <t>1</t>
   </si>
   <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>10014292</t>
+  </si>
+  <si>
+    <t>POP MIE KRI AYM 75G</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>10000861</t>
+  </si>
+  <si>
+    <t>POP MIE BASO 75G</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>20045611</t>
+  </si>
+  <si>
+    <t>SEDAAP MI GRNG CUP85</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>10023791</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE KR.AYAM72</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>20096781</t>
-  </si>
-  <si>
-    <t>SEDAAP MI KR.SPCY 87</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>20136385</t>
-  </si>
-  <si>
-    <t>SEDAAP GRG CHF.DVN93</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>10035852</t>
-  </si>
-  <si>
-    <t>BIHUNKU GRG SPCL 60G</t>
+    <t>20099297</t>
+  </si>
+  <si>
+    <t>SDAAP MIE SP.CHKN 81</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>20093110</t>
-  </si>
-  <si>
-    <t>KUSUKA BALADO 180G</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20120421</t>
-  </si>
-  <si>
-    <t>TARO POTATO BBQ 115G</t>
-  </si>
-  <si>
-    <t>20116675</t>
-  </si>
-  <si>
-    <t>CHTATO LITE NORI 115</t>
+    <t>20104077</t>
+  </si>
+  <si>
+    <t>SEDAP KCP SPCL 725G</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>10022534</t>
+  </si>
+  <si>
+    <t>ABC KCP MNS PCH685G</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>20114757</t>
+  </si>
+  <si>
+    <t>GURIBEE RMP.LAUT 65G</t>
   </si>
   <si>
     <t>RT,(E-14H)</t>
   </si>
   <si>
-    <t>20136007</t>
-  </si>
-  <si>
-    <t>MR.POTATO BBQ 85G</t>
-  </si>
-  <si>
-    <t>20135539</t>
-  </si>
-  <si>
-    <t>MR.POTATO ORGINAL85G</t>
-  </si>
-  <si>
-    <t>20013662</t>
-  </si>
-  <si>
-    <t>BISKUAT COKLAT121.6G</t>
-  </si>
-  <si>
-    <t>20014537</t>
-  </si>
-  <si>
-    <t>BISKUAT ORIGNAL121.6</t>
-  </si>
-  <si>
-    <t>20044008</t>
-  </si>
-  <si>
-    <t>BENG-BENG MAXX 32G</t>
-  </si>
-  <si>
-    <t>20135198</t>
-  </si>
-  <si>
-    <t>WONHAE YOG.GUM ORI48</t>
-  </si>
-  <si>
-    <t>20052630</t>
-  </si>
-  <si>
-    <t>LOTTE CHOCO PIE 156G</t>
-  </si>
-  <si>
-    <t>10008550</t>
-  </si>
-  <si>
-    <t>G/T CHOCHP DB.CHO 72</t>
-  </si>
-  <si>
-    <t>10000461</t>
-  </si>
-  <si>
-    <t>MONDE SERENA GOLD 50</t>
-  </si>
-  <si>
-    <t>20098348</t>
-  </si>
-  <si>
-    <t>REBO KUACI ORIGNL120</t>
-  </si>
-  <si>
-    <t>10029542</t>
-  </si>
-  <si>
-    <t>MR.BREAD COKLAT KEJU</t>
+    <t>20114756</t>
+  </si>
+  <si>
+    <t>GURIBEE BBQ BLDO 65G</t>
+  </si>
+  <si>
+    <t>20004229</t>
+  </si>
+  <si>
+    <t>SMAX RING CHEESE 40G</t>
+  </si>
+  <si>
+    <t>20064426</t>
+  </si>
+  <si>
+    <t>TWISTKO JGNG BKR 70G</t>
+  </si>
+  <si>
+    <t>20056977</t>
+  </si>
+  <si>
+    <t>GARUDA ROSTA BWG 95</t>
+  </si>
+  <si>
+    <t>20095753</t>
+  </si>
+  <si>
+    <t>GRUDA ROSTA WGYU 95</t>
+  </si>
+  <si>
+    <t>10006131</t>
+  </si>
+  <si>
+    <t>AIM ROASTED CORN 180</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>10003144</t>
+  </si>
+  <si>
+    <t>MONDE BOURBON CHO140</t>
+  </si>
+  <si>
+    <t>20039648</t>
+  </si>
+  <si>
+    <t>LOTTE PEPERO ALMND32</t>
+  </si>
+  <si>
+    <t>20025508</t>
+  </si>
+  <si>
+    <t>PIA 100 KCG HJ 138G</t>
+  </si>
+  <si>
+    <t>10000757</t>
+  </si>
+  <si>
+    <t>L'AGIE FULL MILK 60G</t>
+  </si>
+  <si>
+    <t>10010192</t>
+  </si>
+  <si>
+    <t>S/Q CHOCO CASHEW 22G</t>
+  </si>
+  <si>
+    <t>20134686</t>
+  </si>
+  <si>
+    <t>IDM KCG PISTACHIO 55</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20066374</t>
+  </si>
+  <si>
+    <t>IDM MIX NUTS 80G</t>
+  </si>
+  <si>
+    <t>20020008</t>
+  </si>
+  <si>
+    <t>MR.BREAD MANIS CHO 4</t>
   </si>
   <si>
     <t>RT,(E-1H)</t>
@@ -170,6 +200,33 @@
   </si>
   <si>
     <t>PUCUK/H TEH L/SGR350</t>
+  </si>
+  <si>
+    <t>20134691</t>
+  </si>
+  <si>
+    <t>TWB CRACKR RAINBOW57</t>
+  </si>
+  <si>
+    <t>RT,(E-1.5B)</t>
+  </si>
+  <si>
+    <t>20139392</t>
+  </si>
+  <si>
+    <t>BRINGZ LMIER BTR 100</t>
+  </si>
+  <si>
+    <t>10003507</t>
+  </si>
+  <si>
+    <t>MR.P KACANG MADU 80G</t>
+  </si>
+  <si>
+    <t>20129961</t>
+  </si>
+  <si>
+    <t>MR.POTATO ORG KLG 35</t>
   </si>
 </sst>
 </file>
@@ -562,14 +619,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -669,15 +726,15 @@
         <v>14</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -686,58 +743,58 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -746,18 +803,18 @@
         <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -766,18 +823,18 @@
         <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -786,38 +843,38 @@
         <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
@@ -826,18 +883,18 @@
         <v>11</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
@@ -846,18 +903,18 @@
         <v>11</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
@@ -866,47 +923,47 @@
         <v>11</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F16" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>5</v>
@@ -914,10 +971,10 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
@@ -926,18 +983,18 @@
         <v>14</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
@@ -946,70 +1003,210 @@
         <v>14</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>48</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E22" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="F25" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="1" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/E/EG1B.xlsx
+++ b/E/EG1B.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="69">
   <si>
     <t/>
   </si>
   <si>
-    <t>10000975</t>
-  </si>
-  <si>
-    <t>POP MIE AYAM 75G</t>
+    <t>20140802</t>
+  </si>
+  <si>
+    <t>IDM TISU DAPUR 1+1</t>
   </si>
   <si>
     <t>EG1B</t>
@@ -28,205 +28,196 @@
     <t>1</t>
   </si>
   <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20096641</t>
+  </si>
+  <si>
+    <t>IDM FRSHNS ORANGE 50</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20134460</t>
+  </si>
+  <si>
+    <t>MEGA PKEMON POKEBALL</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>20134458</t>
+  </si>
+  <si>
+    <t>T&amp;F PLSTC ENGINE ASS</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>20130447</t>
+  </si>
+  <si>
+    <t>TOS TOS TRTCS RC140</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20128517</t>
+  </si>
+  <si>
+    <t>TOS TOS TRTCS KB140</t>
+  </si>
+  <si>
+    <t>20141464</t>
+  </si>
+  <si>
+    <t>RMN YES HKTA CHKN88G</t>
+  </si>
+  <si>
+    <t>20141466</t>
+  </si>
+  <si>
+    <t>RMN YES TKYO CHKN84G</t>
+  </si>
+  <si>
+    <t>20063488</t>
+  </si>
+  <si>
+    <t>ROMA ARDEN CHOCO 72G</t>
+  </si>
+  <si>
+    <t>20063093</t>
+  </si>
+  <si>
+    <t>DELFI MALTITOS 26</t>
+  </si>
+  <si>
+    <t>20142332</t>
+  </si>
+  <si>
+    <t>LARIST CHOCO EGG 20G</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20115549</t>
+  </si>
+  <si>
+    <t>FIBE MINI 100ML</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20055762</t>
+  </si>
+  <si>
+    <t>JELE COLLAGEN 150G</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>20122808</t>
+  </si>
+  <si>
+    <t>MAMAKOKO SANTAN 65ML</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>20025508</t>
+  </si>
+  <si>
+    <t>PIA 100 KCG HJ 138G</t>
+  </si>
+  <si>
+    <t>10000757</t>
+  </si>
+  <si>
+    <t>L'AGIE FULL MILK 60G</t>
+  </si>
+  <si>
+    <t>10010192</t>
+  </si>
+  <si>
+    <t>S/Q CHOCO CASHEW 22G</t>
+  </si>
+  <si>
+    <t>20134686</t>
+  </si>
+  <si>
+    <t>IDM KCG PISTACHIO 55</t>
+  </si>
+  <si>
+    <t>20066374</t>
+  </si>
+  <si>
+    <t>IDM MIX NUTS 80G</t>
+  </si>
+  <si>
+    <t>20020008</t>
+  </si>
+  <si>
+    <t>MR.BREAD MANIS CHO 4</t>
+  </si>
+  <si>
+    <t>RT,(E-1H)</t>
+  </si>
+  <si>
+    <t>20035484</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH MLATI350</t>
+  </si>
+  <si>
+    <t>20048155</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH L/SGR350</t>
+  </si>
+  <si>
+    <t>20134691</t>
+  </si>
+  <si>
+    <t>TWB CRACKR RAINBOW57</t>
+  </si>
+  <si>
+    <t>RT,(E-1.5B)</t>
+  </si>
+  <si>
+    <t>20139392</t>
+  </si>
+  <si>
+    <t>BRINGZ LMIER BTR 100</t>
+  </si>
+  <si>
+    <t>10003507</t>
+  </si>
+  <si>
+    <t>MR.P KACANG MADU 80G</t>
+  </si>
+  <si>
     <t>RT,(E-2B)</t>
   </si>
   <si>
-    <t>10014292</t>
-  </si>
-  <si>
-    <t>POP MIE KRI AYM 75G</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>10000861</t>
-  </si>
-  <si>
-    <t>POP MIE BASO 75G</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>20045611</t>
-  </si>
-  <si>
-    <t>SEDAAP MI GRNG CUP85</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20099297</t>
-  </si>
-  <si>
-    <t>SDAAP MIE SP.CHKN 81</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>20104077</t>
-  </si>
-  <si>
-    <t>SEDAP KCP SPCL 725G</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>10022534</t>
-  </si>
-  <si>
-    <t>ABC KCP MNS PCH685G</t>
+    <t>20129961</t>
+  </si>
+  <si>
+    <t>MR.POTATO ORG KLG 35</t>
   </si>
   <si>
     <t>7</t>
-  </si>
-  <si>
-    <t>20114757</t>
-  </si>
-  <si>
-    <t>GURIBEE RMP.LAUT 65G</t>
-  </si>
-  <si>
-    <t>RT,(E-14H)</t>
-  </si>
-  <si>
-    <t>20114756</t>
-  </si>
-  <si>
-    <t>GURIBEE BBQ BLDO 65G</t>
-  </si>
-  <si>
-    <t>20004229</t>
-  </si>
-  <si>
-    <t>SMAX RING CHEESE 40G</t>
-  </si>
-  <si>
-    <t>20064426</t>
-  </si>
-  <si>
-    <t>TWISTKO JGNG BKR 70G</t>
-  </si>
-  <si>
-    <t>20056977</t>
-  </si>
-  <si>
-    <t>GARUDA ROSTA BWG 95</t>
-  </si>
-  <si>
-    <t>20095753</t>
-  </si>
-  <si>
-    <t>GRUDA ROSTA WGYU 95</t>
-  </si>
-  <si>
-    <t>10006131</t>
-  </si>
-  <si>
-    <t>AIM ROASTED CORN 180</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>10003144</t>
-  </si>
-  <si>
-    <t>MONDE BOURBON CHO140</t>
-  </si>
-  <si>
-    <t>20039648</t>
-  </si>
-  <si>
-    <t>LOTTE PEPERO ALMND32</t>
-  </si>
-  <si>
-    <t>20025508</t>
-  </si>
-  <si>
-    <t>PIA 100 KCG HJ 138G</t>
-  </si>
-  <si>
-    <t>10000757</t>
-  </si>
-  <si>
-    <t>L'AGIE FULL MILK 60G</t>
-  </si>
-  <si>
-    <t>10010192</t>
-  </si>
-  <si>
-    <t>S/Q CHOCO CASHEW 22G</t>
-  </si>
-  <si>
-    <t>20134686</t>
-  </si>
-  <si>
-    <t>IDM KCG PISTACHIO 55</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20066374</t>
-  </si>
-  <si>
-    <t>IDM MIX NUTS 80G</t>
-  </si>
-  <si>
-    <t>20020008</t>
-  </si>
-  <si>
-    <t>MR.BREAD MANIS CHO 4</t>
-  </si>
-  <si>
-    <t>RT,(E-1H)</t>
-  </si>
-  <si>
-    <t>20035484</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH MLATI350</t>
-  </si>
-  <si>
-    <t>20048155</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH L/SGR350</t>
-  </si>
-  <si>
-    <t>20134691</t>
-  </si>
-  <si>
-    <t>TWB CRACKR RAINBOW57</t>
-  </si>
-  <si>
-    <t>RT,(E-1.5B)</t>
-  </si>
-  <si>
-    <t>20139392</t>
-  </si>
-  <si>
-    <t>BRINGZ LMIER BTR 100</t>
-  </si>
-  <si>
-    <t>10003507</t>
-  </si>
-  <si>
-    <t>MR.P KACANG MADU 80G</t>
-  </si>
-  <si>
-    <t>20129961</t>
-  </si>
-  <si>
-    <t>MR.POTATO ORG KLG 35</t>
   </si>
 </sst>
 </file>
@@ -619,7 +610,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -686,15 +677,15 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -703,7 +694,7 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>5</v>
@@ -711,10 +702,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -723,10 +714,10 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -740,13 +731,13 @@
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="F6" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -760,41 +751,41 @@
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -803,110 +794,110 @@
         <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="F11" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="C14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="F14" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -920,13 +911,13 @@
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -940,13 +931,13 @@
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -960,13 +951,13 @@
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -980,13 +971,13 @@
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1000,13 +991,13 @@
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1020,13 +1011,13 @@
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -1040,10 +1031,10 @@
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>53</v>
@@ -1060,13 +1051,13 @@
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1080,33 +1071,33 @@
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="C24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F24" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1120,13 +1111,13 @@
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1140,10 +1131,10 @@
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>65</v>
@@ -1160,53 +1151,13 @@
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/E/EG1B.xlsx
+++ b/E/EG1B.xlsx
@@ -82,13 +82,13 @@
     <t>10029724</t>
   </si>
   <si>
-    <t>GARUDA KCNG ATOM 100</t>
+    <t>GARUDA KCNG ATOM 95</t>
   </si>
   <si>
     <t>10003840</t>
   </si>
   <si>
-    <t>GARUDA KCG.TELUR 110</t>
+    <t>GARUDA KCG.TELUR 100</t>
   </si>
   <si>
     <t>10036934</t>

--- a/E/EG1B.xlsx
+++ b/E/EG1B.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="67">
   <si>
     <t/>
   </si>
   <si>
-    <t>20036197</t>
-  </si>
-  <si>
-    <t>COCA COLA PET 1 LT</t>
+    <t>20027167</t>
+  </si>
+  <si>
+    <t>IDM FAC.TISSUE NP400</t>
   </si>
   <si>
     <t>EG1B</t>
@@ -28,178 +28,127 @@
     <t>1</t>
   </si>
   <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20131516</t>
+  </si>
+  <si>
+    <t>LARIST DET.FRS BT450</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>20007929</t>
+  </si>
+  <si>
+    <t>MATCHBOX MOBIL 30782</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20028329</t>
+  </si>
+  <si>
+    <t>H.WHL COLOUR SHIFTER</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>20142495</t>
+  </si>
+  <si>
+    <t>INDOMARET AIR MIN 1L</t>
+  </si>
+  <si>
+    <t>20138894</t>
+  </si>
+  <si>
+    <t>AMO FIZZY EASY 200ML</t>
+  </si>
+  <si>
+    <t>20138893</t>
+  </si>
+  <si>
+    <t>AMO DRMY STRAW 200ML</t>
+  </si>
+  <si>
+    <t>20021032</t>
+  </si>
+  <si>
+    <t>QTELA KERIPIK BLD 60</t>
+  </si>
+  <si>
     <t>RT,(E-14H)</t>
   </si>
   <si>
-    <t>20036200</t>
-  </si>
-  <si>
-    <t>SPRITE SOFT DRINK 1L</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>20036199</t>
-  </si>
-  <si>
-    <t>FANTA STRAWBERRY 1 L</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>20005530</t>
-  </si>
-  <si>
-    <t>NESTLE PURE LIFE 1.5</t>
-  </si>
-  <si>
-    <t>4</t>
+    <t>20012679</t>
+  </si>
+  <si>
+    <t>QTELA KRIPIK BBQ 60</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>20012678</t>
+  </si>
+  <si>
+    <t>QTELA KERIPIK ORG 60</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>20063488</t>
+  </si>
+  <si>
+    <t>ROMA ARDEN CHOCO 72G</t>
   </si>
   <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20090527</t>
-  </si>
-  <si>
-    <t>CRYSTALIN BTL 600mL</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>20142819</t>
-  </si>
-  <si>
-    <t>EWATER LEMON 555ML</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20142818</t>
-  </si>
-  <si>
-    <t>EWATER GRAPEFRT 555</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>20065778</t>
-  </si>
-  <si>
-    <t>COCA COLA PET 390 ML</t>
-  </si>
-  <si>
-    <t>20065780</t>
-  </si>
-  <si>
-    <t>FANTA STRW PET 390ML</t>
-  </si>
-  <si>
-    <t>20065779</t>
-  </si>
-  <si>
-    <t>SPRITE PET 390 ML</t>
-  </si>
-  <si>
-    <t>20135311</t>
-  </si>
-  <si>
-    <t>HYDROPL ISTNC JRK350</t>
-  </si>
-  <si>
-    <t>20142863</t>
-  </si>
-  <si>
-    <t>EWATER LEMON 380</t>
-  </si>
-  <si>
-    <t>20142862</t>
-  </si>
-  <si>
-    <t>EWATER GRPFRT 380</t>
-  </si>
-  <si>
-    <t>10007380</t>
-  </si>
-  <si>
-    <t>ULTRA SLIM COKLAT200</t>
-  </si>
-  <si>
-    <t>10008095</t>
-  </si>
-  <si>
-    <t>ULTRA SLIM STRAW 200</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>20088964</t>
-  </si>
-  <si>
-    <t>ULTRA SUSU TARO 200</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>20138895</t>
-  </si>
-  <si>
-    <t>ULTRA UHT BLUBRY 200</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>20143260</t>
-  </si>
-  <si>
-    <t>KUSUKA UBI MADU 42G</t>
-  </si>
-  <si>
-    <t>20037179</t>
-  </si>
-  <si>
-    <t>HAPPYTOS CHP R.CRN55</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20072575</t>
-  </si>
-  <si>
-    <t>KRISBEE F.FRIES 65G</t>
-  </si>
-  <si>
-    <t>RT,(E-0.5B)</t>
-  </si>
-  <si>
-    <t>20137880</t>
-  </si>
-  <si>
-    <t>IDM KACANG KRIUK 95G</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20141098</t>
-  </si>
-  <si>
-    <t>MR PTT BULDAK CHES40</t>
-  </si>
-  <si>
-    <t>20139841</t>
-  </si>
-  <si>
-    <t>MR POTATO CRBNARA 40</t>
+    <t>20142943</t>
+  </si>
+  <si>
+    <t>IDM CHOCO CRACKR 100</t>
+  </si>
+  <si>
+    <t>20142944</t>
+  </si>
+  <si>
+    <t>IDM CHOCO WAFER 120</t>
+  </si>
+  <si>
+    <t>20092546</t>
+  </si>
+  <si>
+    <t>SLVR QUEEN MATCHA 22</t>
+  </si>
+  <si>
+    <t>20011850</t>
+  </si>
+  <si>
+    <t>OB HERBAL OBT BTK 60</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20124758</t>
+  </si>
+  <si>
+    <t>OB/HRBL HBTSAUDA 60</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
   </si>
   <si>
     <t>20143286</t>
@@ -224,9 +173,6 @@
   </si>
   <si>
     <t>REGAL MARIE 120GR</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
   </si>
   <si>
     <t>20129863</t>
@@ -658,15 +604,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="3" customWidth="1"/>
-    <col min="5" max="5" width="4" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="4" max="5" width="3" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -746,15 +691,15 @@
         <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -763,10 +708,10 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -780,61 +725,61 @@
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="F6" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -843,18 +788,18 @@
         <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -863,18 +808,18 @@
         <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -883,10 +828,10 @@
         <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -900,133 +845,133 @@
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1040,13 +985,13 @@
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1060,293 +1005,153 @@
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E20" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="F20" s="1" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>15</v>
+        <v>58</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
